--- a/docs/1.Envisioning/other/Аналіз проектних ризиків.xlsx
+++ b/docs/1.Envisioning/other/Аналіз проектних ризиків.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Documents\Practice-2023\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\3 КУРС\ТРПЗ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4878E1C5-C3F6-49B0-82DE-E2F02253FEE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012E7379-E100-4529-80C5-A94D7B1A75C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="73">
   <si>
     <t>#</t>
   </si>
@@ -67,33 +66,201 @@
     <t>Відповідальний</t>
   </si>
   <si>
-    <t>Vlad Kyshynets</t>
-  </si>
-  <si>
-    <t>Костя Орлеан</t>
-  </si>
-  <si>
-    <t>Ангеліна Бабич</t>
-  </si>
-  <si>
-    <t>Евгений Шабля</t>
-  </si>
-  <si>
-    <t>Илья Рыжий</t>
-  </si>
-  <si>
-    <t>Вадим Алдик</t>
-  </si>
-  <si>
     <t>УВАГА! 
 Перш ніж заповнювати цю таблицю замініть прізвища на листі "Люди" аби мати змогу обирати їх у графі "Відповідальний"!</t>
+  </si>
+  <si>
+    <t>Приходько С.С.</t>
+  </si>
+  <si>
+    <t>Ленко А.Е.</t>
+  </si>
+  <si>
+    <t>Ватутіна Д.Є.</t>
+  </si>
+  <si>
+    <t>Павлій С.С.</t>
+  </si>
+  <si>
+    <t>Абоімов В.П.</t>
+  </si>
+  <si>
+    <t>Рубан О.Ю.</t>
+  </si>
+  <si>
+    <t>Полиба Я.В.</t>
+  </si>
+  <si>
+    <t>Дерієнко В.В.</t>
+  </si>
+  <si>
+    <t>Жеребко О.А.</t>
+  </si>
+  <si>
+    <t>Мірошніченко В.О.</t>
+  </si>
+  <si>
+    <t>Шостак М.С.</t>
+  </si>
+  <si>
+    <t>Пилипенко О.О.</t>
+  </si>
+  <si>
+    <t>Сервер недоступний</t>
+  </si>
+  <si>
+    <t>Помилки API</t>
+  </si>
+  <si>
+    <t>Помилка підключення до PostgreSQL</t>
+  </si>
+  <si>
+    <t>Втрата даних у БД</t>
+  </si>
+  <si>
+    <t>SQL помилки або неправильні запити</t>
+  </si>
+  <si>
+    <t>Повільні запити до БД</t>
+  </si>
+  <si>
+    <t>Неправильна робота Markdown рендеру</t>
+  </si>
+  <si>
+    <t>Проблеми адаптивності UI</t>
+  </si>
+  <si>
+    <t>Помилки експорту .md</t>
+  </si>
+  <si>
+    <t>Проблеми авторизації або доступу</t>
+  </si>
+  <si>
+    <t>користувач не може отримати нотатки</t>
+  </si>
+  <si>
+    <t>нотатки не зберігаються</t>
+  </si>
+  <si>
+    <t>дані не записуються</t>
+  </si>
+  <si>
+    <t>нотатки зникають</t>
+  </si>
+  <si>
+    <t>пошкодження даних</t>
+  </si>
+  <si>
+    <t>повільна робота застосунку</t>
+  </si>
+  <si>
+    <t>текст відображається некоректно</t>
+  </si>
+  <si>
+    <t>поганий UX на мобільних</t>
+  </si>
+  <si>
+    <t>користувач не може завантажити файл</t>
+  </si>
+  <si>
+    <t>користувач не може працювати з нотатками</t>
+  </si>
+  <si>
+    <t>моніторинг сервера</t>
+  </si>
+  <si>
+    <t>тестування API</t>
+  </si>
+  <si>
+    <t>перевірка конфігурації</t>
+  </si>
+  <si>
+    <t>резервні копії</t>
+  </si>
+  <si>
+    <t>code review</t>
+  </si>
+  <si>
+    <t>оптимізація індексів</t>
+  </si>
+  <si>
+    <t>використання стабільної бібліотеки</t>
+  </si>
+  <si>
+    <t>responsive дизайн</t>
+  </si>
+  <si>
+    <t>тестування функції експорту</t>
+  </si>
+  <si>
+    <t>тестування безпеки</t>
+  </si>
+  <si>
+    <t>перезапуск сервера</t>
+  </si>
+  <si>
+    <t>виправлення endpoint</t>
+  </si>
+  <si>
+    <t>відновлення з'єднання</t>
+  </si>
+  <si>
+    <t>відновлення backup</t>
+  </si>
+  <si>
+    <t>виправлення запитів</t>
+  </si>
+  <si>
+    <t>оптимізація SQL</t>
+  </si>
+  <si>
+    <t>оновлення бібліотеки</t>
+  </si>
+  <si>
+    <t>переробка CSS</t>
+  </si>
+  <si>
+    <t>виправлення генерації файлу</t>
+  </si>
+  <si>
+    <t>відновлення доступу</t>
+  </si>
+  <si>
+    <t>відсутність відповіді API</t>
+  </si>
+  <si>
+    <t>HTTP помилки</t>
+  </si>
+  <si>
+    <t>database connection error</t>
+  </si>
+  <si>
+    <t>відсутні записи</t>
+  </si>
+  <si>
+    <t>SQL exception</t>
+  </si>
+  <si>
+    <t>затримка відповіді</t>
+  </si>
+  <si>
+    <t>помилки форматування</t>
+  </si>
+  <si>
+    <t>неправильне відображення</t>
+  </si>
+  <si>
+    <t>помилка скачування</t>
+  </si>
+  <si>
+    <t>login error</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -118,12 +285,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -146,7 +307,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -154,24 +315,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -391,7 +591,7 @@
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" customWidth="1"/>
     <col min="4" max="4" width="11.5703125" customWidth="1"/>
     <col min="5" max="5" width="11.42578125" customWidth="1"/>
@@ -403,460 +603,490 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
+    <row r="2" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="B2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="E2" s="7">
+        <v>5</v>
+      </c>
+      <c r="F2" s="7">
         <f t="shared" ref="F2:F21" si="0">D2*E2</f>
-        <v>0</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-    </row>
-    <row r="3" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
+      <c r="G2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="7">
+        <v>5</v>
+      </c>
+      <c r="F3" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="B4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="E4" s="7">
+        <v>5</v>
+      </c>
+      <c r="F4" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
+      <c r="B5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="E5" s="7">
+        <v>5</v>
+      </c>
+      <c r="F5" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
+      <c r="B6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="E6" s="7">
+        <v>4</v>
+      </c>
+      <c r="F6" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
+      <c r="B7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="E7" s="7">
+        <v>3</v>
+      </c>
+      <c r="F7" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-    </row>
-    <row r="8" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
+      <c r="B8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="E8" s="7">
+        <v>3</v>
+      </c>
+      <c r="F8" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-    </row>
-    <row r="9" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
+      <c r="B9" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="E9" s="7">
+        <v>3</v>
+      </c>
+      <c r="F9" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-    </row>
-    <row r="10" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
+      <c r="B10" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="E10" s="7">
+        <v>3</v>
+      </c>
+      <c r="F10" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
+      <c r="B11" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="E11" s="7">
+        <v>4</v>
+      </c>
+      <c r="F11" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+      <c r="A12" s="1"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
+      <c r="A13" s="1"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
+      <c r="A14" s="1"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+      <c r="A15" s="1"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
+      <c r="A16" s="1"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
+      <c r="A18" s="1"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="A19" s="1"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
+      <c r="A20" s="1"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="2">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2">
-        <v>0</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
+      <c r="A21" s="1"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
-        <v>16</v>
+      <c r="A25" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -864,7 +1094,7 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Оберіть зі спику члена команди" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>Люди!$A$1:$A$6</xm:f>
@@ -882,40 +1112,70 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>10</v>
+      <c r="A1" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>15</v>
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/docs/1.Envisioning/other/Аналіз проектних ризиків.xlsx
+++ b/docs/1.Envisioning/other/Аналіз проектних ризиків.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\3 КУРС\ТРПЗ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012E7379-E100-4529-80C5-A94D7B1A75C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDC2827-C2B0-4A81-9BB2-6AE28C3BF278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ризики" sheetId="1" r:id="rId1"/>
@@ -293,7 +293,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -306,8 +306,14 @@
         <bgColor rgb="FF666666"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -330,31 +336,121 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -363,17 +459,469 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF666666"/>
+          <bgColor rgb="FF666666"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -384,6 +932,30 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83885570-DEE9-4D58-ACA9-EBA411654F41}" name="Table1" displayName="Table1" ref="A1:J11" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="12" tableBorderDxfId="13" totalsRowBorderDxfId="11">
+  <autoFilter ref="A1:J11" xr:uid="{83885570-DEE9-4D58-ACA9-EBA411654F41}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J11">
+    <sortCondition descending="1" ref="F1:F11"/>
+  </sortState>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{DFCC87EC-FE86-4433-971B-8D2B841A9CB4}" name="#" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{9C58E689-3884-4D37-A386-66E50E643E57}" name="Умова" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{BBEAE54E-EFA0-4E9D-A308-26EF1E8FE5A7}" name="Наслідки" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{95E48028-63BF-4D48-9ACA-B10CF2ACFABC}" name="Ймовірність_x000a_(0-1)" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{0AE16713-C860-47C7-96C5-7F593A667A23}" name="Загроза_x000a_(1-5)" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{CDE629D0-1BCC-42D6-B489-46BD9041565E}" name="Очікуваний вплив" dataDxfId="5">
+      <calculatedColumnFormula>D2*E2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{5ADE323C-C3CD-4090-BE41-0CEC875A14B1}" name="Попередження" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{A0910F2B-5267-49AC-AC85-9E0531E099C4}" name="Реагування" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{1D34F96A-B04C-4415-898C-43DC4827B4C9}" name="Тригер" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{5B64BD07-480B-41B6-AE63-ADAC466E5E6D}" name="Відповідальний" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -595,7 +1167,7 @@
     <col min="3" max="3" width="18.85546875" customWidth="1"/>
     <col min="4" max="4" width="11.5703125" customWidth="1"/>
     <col min="5" max="5" width="11.42578125" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
     <col min="7" max="7" width="21.28515625" customWidth="1"/>
     <col min="8" max="8" width="18.28515625" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" customWidth="1"/>
@@ -603,328 +1175,328 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="15" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="7">
+      <c r="A2" s="22">
+        <v>2</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="25">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="25">
+        <v>5</v>
+      </c>
+      <c r="F2" s="25">
+        <f>D2*E2</f>
+        <v>2.5</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" s="28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="22">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B3" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C3" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D3" s="25">
         <v>0.4</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E3" s="25">
         <v>5</v>
       </c>
-      <c r="F2" s="7">
-        <f t="shared" ref="F2:F21" si="0">D2*E2</f>
+      <c r="F3" s="25">
+        <f>D3*E3</f>
         <v>2</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G3" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H3" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I3" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J3" s="28" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="7">
+    <row r="4" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="22">
+        <v>3</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="25">
+        <v>0.4</v>
+      </c>
+      <c r="E4" s="25">
+        <v>5</v>
+      </c>
+      <c r="F4" s="25">
+        <f>D4*E4</f>
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="E3" s="7">
+      <c r="G4" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="22">
+        <v>8</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="25">
+        <v>0.4</v>
+      </c>
+      <c r="E5" s="25">
+        <v>3</v>
+      </c>
+      <c r="F5" s="25">
+        <f>D5*E5</f>
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="22">
         <v>5</v>
       </c>
-      <c r="F3" s="7">
-        <f t="shared" si="0"/>
-        <v>2.5</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="J3" s="12" t="s">
+      <c r="B6" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="E6" s="25">
+        <v>4</v>
+      </c>
+      <c r="F6" s="25">
+        <f>D6*E6</f>
+        <v>1.2</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="J6" s="28" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="7">
+    <row r="7" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="11">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="E7" s="6">
+        <v>5</v>
+      </c>
+      <c r="F7" s="6">
+        <f>D7*E7</f>
+        <v>1</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A8" s="11">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="E8" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="7">
-        <v>0.4</v>
-      </c>
-      <c r="E4" s="7">
-        <v>5</v>
-      </c>
-      <c r="F4" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="E5" s="7">
-        <v>5</v>
-      </c>
-      <c r="F5" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="7">
+      <c r="F8" s="6">
+        <f>D8*E8</f>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="11">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="6">
         <v>0.3</v>
       </c>
-      <c r="E6" s="7">
-        <v>4</v>
-      </c>
-      <c r="F6" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="7">
+      <c r="E9" s="6">
+        <v>3</v>
+      </c>
+      <c r="F9" s="6">
+        <f>D9*E9</f>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="11">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="6">
         <v>0.3</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E10" s="6">
         <v>3</v>
       </c>
-      <c r="F7" s="7">
-        <f t="shared" si="0"/>
+      <c r="F10" s="6">
+        <f>D10*E10</f>
         <v>0.89999999999999991</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="7">
-        <v>7</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="7">
-        <v>0.3</v>
-      </c>
-      <c r="E8" s="7">
-        <v>3</v>
-      </c>
-      <c r="F8" s="7">
-        <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="7">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="7">
-        <v>0.4</v>
-      </c>
-      <c r="E9" s="7">
-        <v>3</v>
-      </c>
-      <c r="F9" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="7">
-        <v>9</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="7">
-        <v>0.3</v>
-      </c>
-      <c r="E10" s="7">
-        <v>3</v>
-      </c>
-      <c r="F10" s="7">
-        <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="9" t="s">
         <v>71</v>
       </c>
       <c r="J10" s="12" t="s">
@@ -932,35 +1504,35 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A11" s="7">
+      <c r="A11" s="16">
         <v>10</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="18">
         <v>0.2</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="18">
         <v>4</v>
       </c>
-      <c r="F11" s="7">
-        <f t="shared" si="0"/>
+      <c r="F11" s="18">
+        <f>D11*E11</f>
         <v>0.8</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="21" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1092,6 +1664,9 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -1118,32 +1693,32 @@
     <col min="1" max="1" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>

--- a/docs/1.Envisioning/other/Аналіз проектних ризиків.xlsx
+++ b/docs/1.Envisioning/other/Аналіз проектних ризиків.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDC2827-C2B0-4A81-9BB2-6AE28C3BF278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D12384D-BF8C-48E7-AA4A-B84ADED2E6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5550" yWindow="3270" windowWidth="22470" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ризики" sheetId="1" r:id="rId1"/>
@@ -518,9 +518,375 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="14">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -555,372 +921,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -935,24 +935,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83885570-DEE9-4D58-ACA9-EBA411654F41}" name="Table1" displayName="Table1" ref="A1:J11" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="12" tableBorderDxfId="13" totalsRowBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83885570-DEE9-4D58-ACA9-EBA411654F41}" name="Table1" displayName="Table1" ref="A1:J11" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="A1:J11" xr:uid="{83885570-DEE9-4D58-ACA9-EBA411654F41}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J11">
     <sortCondition descending="1" ref="F1:F11"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{DFCC87EC-FE86-4433-971B-8D2B841A9CB4}" name="#" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{9C58E689-3884-4D37-A386-66E50E643E57}" name="Умова" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{BBEAE54E-EFA0-4E9D-A308-26EF1E8FE5A7}" name="Наслідки" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{95E48028-63BF-4D48-9ACA-B10CF2ACFABC}" name="Ймовірність_x000a_(0-1)" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{0AE16713-C860-47C7-96C5-7F593A667A23}" name="Загроза_x000a_(1-5)" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{CDE629D0-1BCC-42D6-B489-46BD9041565E}" name="Очікуваний вплив" dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{DFCC87EC-FE86-4433-971B-8D2B841A9CB4}" name="#" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{9C58E689-3884-4D37-A386-66E50E643E57}" name="Умова" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{BBEAE54E-EFA0-4E9D-A308-26EF1E8FE5A7}" name="Наслідки" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{95E48028-63BF-4D48-9ACA-B10CF2ACFABC}" name="Ймовірність_x000a_(0-1)" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{0AE16713-C860-47C7-96C5-7F593A667A23}" name="Загроза_x000a_(1-5)" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{CDE629D0-1BCC-42D6-B489-46BD9041565E}" name="Очікуваний вплив" dataDxfId="4">
       <calculatedColumnFormula>D2*E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{5ADE323C-C3CD-4090-BE41-0CEC875A14B1}" name="Попередження" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{A0910F2B-5267-49AC-AC85-9E0531E099C4}" name="Реагування" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{1D34F96A-B04C-4415-898C-43DC4827B4C9}" name="Тригер" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{5B64BD07-480B-41B6-AE63-ADAC466E5E6D}" name="Відповідальний" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{5ADE323C-C3CD-4090-BE41-0CEC875A14B1}" name="Попередження" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{A0910F2B-5267-49AC-AC85-9E0531E099C4}" name="Реагування" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{1D34F96A-B04C-4415-898C-43DC4827B4C9}" name="Тригер" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{5B64BD07-480B-41B6-AE63-ADAC466E5E6D}" name="Відповідальний" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1223,7 +1223,7 @@
         <v>5</v>
       </c>
       <c r="F2" s="25">
-        <f>D2*E2</f>
+        <f t="shared" ref="F2:F11" si="0">D2*E2</f>
         <v>2.5</v>
       </c>
       <c r="G2" s="26" t="s">
@@ -1256,7 +1256,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="25">
-        <f>D3*E3</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="G3" s="26" t="s">
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F4" s="25">
-        <f>D4*E4</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="G4" s="26" t="s">
@@ -1322,7 +1322,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="25">
-        <f>D5*E5</f>
+        <f t="shared" si="0"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="G5" s="26" t="s">
@@ -1355,7 +1355,7 @@
         <v>4</v>
       </c>
       <c r="F6" s="25">
-        <f>D6*E6</f>
+        <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
       <c r="G6" s="26" t="s">
@@ -1371,7 +1371,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <v>4</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="6">
-        <f>D7*E7</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G7" s="8" t="s">
@@ -1404,7 +1404,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="6">
-        <f>D8*E8</f>
+        <f t="shared" si="0"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="G8" s="8" t="s">
@@ -1437,7 +1437,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="6">
-        <f>D9*E9</f>
+        <f t="shared" si="0"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="G9" s="9" t="s">
@@ -1487,7 +1487,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="6">
-        <f>D10*E10</f>
+        <f t="shared" si="0"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="G10" s="9" t="s">
@@ -1520,7 +1520,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="18">
-        <f>D11*E11</f>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="G11" s="19" t="s">
